--- a/prep_eda/Data/maven_music_listening_history.xlsx
+++ b/prep_eda/Data/maven_music_listening_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alice/Desktop/Course_Materials/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\source\py\ML_python\prep_eda\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F750B49B-9C49-AC49-ADF6-9800A919F7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97553F8D-6788-4643-B8AE-5DF0642B815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16000" activeTab="1" xr2:uid="{E8B08011-257B-A045-9B7E-1A735E91B791}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{E8B08011-257B-A045-9B7E-1A735E91B791}"/>
   </bookViews>
   <sheets>
     <sheet name="listening_history" sheetId="1" r:id="rId1"/>
@@ -205,13 +205,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -219,7 +219,7 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -227,15 +227,22 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -264,10 +271,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -283,7 +290,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -580,7 +587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03E26A1-9387-7449-BBB4-1EFA05A98E03}">
   <dimension ref="A1:E506"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -589,7 +596,7 @@
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5001</v>
       </c>
@@ -623,7 +630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5001</v>
       </c>
@@ -640,7 +647,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -657,7 +664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5001</v>
       </c>
@@ -674,7 +681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5001</v>
       </c>
@@ -691,7 +698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5001</v>
       </c>
@@ -708,7 +715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5001</v>
       </c>
@@ -725,7 +732,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5001</v>
       </c>
@@ -742,7 +749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5001</v>
       </c>
@@ -759,7 +766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>5001</v>
       </c>
@@ -776,7 +783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>5001</v>
       </c>
@@ -793,7 +800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5001</v>
       </c>
@@ -810,7 +817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5001</v>
       </c>
@@ -827,7 +834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5001</v>
       </c>
@@ -844,7 +851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>5001</v>
       </c>
@@ -861,7 +868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>5001</v>
       </c>
@@ -878,7 +885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>5001</v>
       </c>
@@ -895,7 +902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>5001</v>
       </c>
@@ -912,7 +919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>5001</v>
       </c>
@@ -929,7 +936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>5001</v>
       </c>
@@ -946,7 +953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>5001</v>
       </c>
@@ -963,7 +970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>5002</v>
       </c>
@@ -980,7 +987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>5002</v>
       </c>
@@ -997,7 +1004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>5002</v>
       </c>
@@ -1014,7 +1021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>5002</v>
       </c>
@@ -1031,7 +1038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>5002</v>
       </c>
@@ -1048,7 +1055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>5002</v>
       </c>
@@ -1065,7 +1072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>5002</v>
       </c>
@@ -1082,7 +1089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>5004</v>
       </c>
@@ -1099,7 +1106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>5004</v>
       </c>
@@ -1116,7 +1123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>5004</v>
       </c>
@@ -1133,7 +1140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>5004</v>
       </c>
@@ -1150,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>5004</v>
       </c>
@@ -1167,7 +1174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>5004</v>
       </c>
@@ -1184,7 +1191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>5004</v>
       </c>
@@ -1201,7 +1208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>5004</v>
       </c>
@@ -1218,7 +1225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>5004</v>
       </c>
@@ -1235,7 +1242,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>5581</v>
       </c>
@@ -1252,7 +1259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>5001</v>
       </c>
@@ -1269,7 +1276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>5001</v>
       </c>
@@ -1286,7 +1293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>5001</v>
       </c>
@@ -1303,7 +1310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>5001</v>
       </c>
@@ -1320,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>5001</v>
       </c>
@@ -1337,7 +1344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>5001</v>
       </c>
@@ -1354,7 +1361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>5001</v>
       </c>
@@ -1371,7 +1378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>5001</v>
       </c>
@@ -1388,7 +1395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>5002</v>
       </c>
@@ -1405,7 +1412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>5002</v>
       </c>
@@ -1422,7 +1429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>5002</v>
       </c>
@@ -1439,7 +1446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>5002</v>
       </c>
@@ -1456,7 +1463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>5002</v>
       </c>
@@ -1473,7 +1480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>5002</v>
       </c>
@@ -1490,7 +1497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>5002</v>
       </c>
@@ -1507,7 +1514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>5002</v>
       </c>
@@ -1524,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>5002</v>
       </c>
@@ -1541,7 +1548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>5759</v>
       </c>
@@ -1558,7 +1565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>5759</v>
       </c>
@@ -1575,7 +1582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5759</v>
       </c>
@@ -1592,7 +1599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5759</v>
       </c>
@@ -1609,7 +1616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5759</v>
       </c>
@@ -1626,7 +1633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5759</v>
       </c>
@@ -1643,7 +1650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5759</v>
       </c>
@@ -1660,7 +1667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>6092</v>
       </c>
@@ -1677,7 +1684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6092</v>
       </c>
@@ -1694,7 +1701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>6092</v>
       </c>
@@ -1711,7 +1718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>6092</v>
       </c>
@@ -1728,7 +1735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>6092</v>
       </c>
@@ -1745,7 +1752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>5581</v>
       </c>
@@ -1762,7 +1769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>5581</v>
       </c>
@@ -1779,7 +1786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>6584</v>
       </c>
@@ -1796,7 +1803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>6584</v>
       </c>
@@ -1813,7 +1820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>6584</v>
       </c>
@@ -1830,7 +1837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>6584</v>
       </c>
@@ -1847,7 +1854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>6584</v>
       </c>
@@ -1864,7 +1871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>6584</v>
       </c>
@@ -1881,7 +1888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>6584</v>
       </c>
@@ -1898,7 +1905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>6584</v>
       </c>
@@ -1915,7 +1922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>6584</v>
       </c>
@@ -1932,7 +1939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>6584</v>
       </c>
@@ -1949,7 +1956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>6584</v>
       </c>
@@ -1966,7 +1973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>6584</v>
       </c>
@@ -1983,7 +1990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>6584</v>
       </c>
@@ -2000,7 +2007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>6584</v>
       </c>
@@ -2017,7 +2024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>6584</v>
       </c>
@@ -2034,7 +2041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>5001</v>
       </c>
@@ -2051,7 +2058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>5001</v>
       </c>
@@ -2068,7 +2075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>5001</v>
       </c>
@@ -2085,7 +2092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>5001</v>
       </c>
@@ -2102,7 +2109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>5001</v>
       </c>
@@ -2119,7 +2126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>5001</v>
       </c>
@@ -2136,7 +2143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>5002</v>
       </c>
@@ -2153,7 +2160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>5002</v>
       </c>
@@ -2170,7 +2177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>5002</v>
       </c>
@@ -2187,7 +2194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>5001</v>
       </c>
@@ -2204,7 +2211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>5001</v>
       </c>
@@ -2221,7 +2228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>5001</v>
       </c>
@@ -2238,7 +2245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>5001</v>
       </c>
@@ -2255,7 +2262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>5001</v>
       </c>
@@ -2272,7 +2279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>5001</v>
       </c>
@@ -2289,7 +2296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>6822</v>
       </c>
@@ -2306,7 +2313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>6822</v>
       </c>
@@ -2323,7 +2330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>6822</v>
       </c>
@@ -2340,7 +2347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>6822</v>
       </c>
@@ -2357,7 +2364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>6822</v>
       </c>
@@ -2374,7 +2381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>6824</v>
       </c>
@@ -2391,7 +2398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>6824</v>
       </c>
@@ -2408,7 +2415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>6824</v>
       </c>
@@ -2425,7 +2432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>6824</v>
       </c>
@@ -2442,7 +2449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>6824</v>
       </c>
@@ -2459,7 +2466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>6824</v>
       </c>
@@ -2476,7 +2483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>6824</v>
       </c>
@@ -2493,7 +2500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>6824</v>
       </c>
@@ -2510,7 +2517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>6824</v>
       </c>
@@ -2527,7 +2534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>6824</v>
       </c>
@@ -2544,7 +2551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>6824</v>
       </c>
@@ -2561,7 +2568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>6824</v>
       </c>
@@ -2578,7 +2585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>6824</v>
       </c>
@@ -2595,7 +2602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>6824</v>
       </c>
@@ -2612,7 +2619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>6824</v>
       </c>
@@ -2629,7 +2636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>6824</v>
       </c>
@@ -2646,7 +2653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>6824</v>
       </c>
@@ -2663,7 +2670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>6824</v>
       </c>
@@ -2680,7 +2687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>7087</v>
       </c>
@@ -2697,7 +2704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>7087</v>
       </c>
@@ -2714,7 +2721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>5759</v>
       </c>
@@ -2731,7 +2738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>5759</v>
       </c>
@@ -2748,7 +2755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>5759</v>
       </c>
@@ -2765,7 +2772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>5759</v>
       </c>
@@ -2782,7 +2789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>5759</v>
       </c>
@@ -2799,7 +2806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>5759</v>
       </c>
@@ -2816,7 +2823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>5759</v>
       </c>
@@ -2833,7 +2840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>5759</v>
       </c>
@@ -2850,7 +2857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>5581</v>
       </c>
@@ -2867,7 +2874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>5581</v>
       </c>
@@ -2884,7 +2891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>6584</v>
       </c>
@@ -2901,7 +2908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>6584</v>
       </c>
@@ -2918,7 +2925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>6584</v>
       </c>
@@ -2935,7 +2942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>6584</v>
       </c>
@@ -2952,7 +2959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>6584</v>
       </c>
@@ -2969,7 +2976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>6584</v>
       </c>
@@ -2986,7 +2993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>6584</v>
       </c>
@@ -3003,7 +3010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>6584</v>
       </c>
@@ -3020,7 +3027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>6584</v>
       </c>
@@ -3037,7 +3044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>6584</v>
       </c>
@@ -3054,7 +3061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>6584</v>
       </c>
@@ -3071,7 +3078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>6584</v>
       </c>
@@ -3088,7 +3095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>6092</v>
       </c>
@@ -3105,7 +3112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>6092</v>
       </c>
@@ -3122,7 +3129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>6092</v>
       </c>
@@ -3139,7 +3146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>6092</v>
       </c>
@@ -3156,7 +3163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>6822</v>
       </c>
@@ -3173,7 +3180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>6822</v>
       </c>
@@ -3190,7 +3197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>6822</v>
       </c>
@@ -3207,7 +3214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>6822</v>
       </c>
@@ -3224,7 +3231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>6822</v>
       </c>
@@ -3241,7 +3248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>6092</v>
       </c>
@@ -3258,7 +3265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>5001</v>
       </c>
@@ -3275,7 +3282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>5001</v>
       </c>
@@ -3292,7 +3299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>5001</v>
       </c>
@@ -3309,7 +3316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>5001</v>
       </c>
@@ -3326,7 +3333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>5001</v>
       </c>
@@ -3343,7 +3350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>5001</v>
       </c>
@@ -3360,7 +3367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>5002</v>
       </c>
@@ -3377,7 +3384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>5002</v>
       </c>
@@ -3394,7 +3401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>5002</v>
       </c>
@@ -3411,7 +3418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>5001</v>
       </c>
@@ -3428,7 +3435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>5001</v>
       </c>
@@ -3445,7 +3452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>5001</v>
       </c>
@@ -3462,7 +3469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>5001</v>
       </c>
@@ -3479,7 +3486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>5001</v>
       </c>
@@ -3496,7 +3503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>5001</v>
       </c>
@@ -3513,7 +3520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>6824</v>
       </c>
@@ -3530,7 +3537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>6824</v>
       </c>
@@ -3547,7 +3554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>6824</v>
       </c>
@@ -3564,7 +3571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>6824</v>
       </c>
@@ -3581,7 +3588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>6824</v>
       </c>
@@ -3598,7 +3605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>6824</v>
       </c>
@@ -3615,7 +3622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>6824</v>
       </c>
@@ -3632,7 +3639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>6824</v>
       </c>
@@ -3649,7 +3656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>7087</v>
       </c>
@@ -3666,7 +3673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>7087</v>
       </c>
@@ -3683,7 +3690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>7087</v>
       </c>
@@ -3700,7 +3707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>7087</v>
       </c>
@@ -3717,7 +3724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>7087</v>
       </c>
@@ -3734,7 +3741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>7087</v>
       </c>
@@ -3751,7 +3758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>7087</v>
       </c>
@@ -3768,7 +3775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>7087</v>
       </c>
@@ -3785,7 +3792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>7087</v>
       </c>
@@ -3802,7 +3809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>5001</v>
       </c>
@@ -3819,7 +3826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>5001</v>
       </c>
@@ -3836,7 +3843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>5001</v>
       </c>
@@ -3853,7 +3860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>5001</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>5001</v>
       </c>
@@ -3887,7 +3894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>5001</v>
       </c>
@@ -3904,7 +3911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>5001</v>
       </c>
@@ -3921,7 +3928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>6822</v>
       </c>
@@ -3938,7 +3945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>6822</v>
       </c>
@@ -3955,7 +3962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>6822</v>
       </c>
@@ -3972,7 +3979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>6822</v>
       </c>
@@ -3989,7 +3996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>6822</v>
       </c>
@@ -4006,7 +4013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>6824</v>
       </c>
@@ -4023,7 +4030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>6824</v>
       </c>
@@ -4040,7 +4047,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>6824</v>
       </c>
@@ -4057,7 +4064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>6824</v>
       </c>
@@ -4074,7 +4081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>6824</v>
       </c>
@@ -4091,7 +4098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>5267</v>
       </c>
@@ -4108,7 +4115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>5267</v>
       </c>
@@ -4125,7 +4132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>5267</v>
       </c>
@@ -4142,7 +4149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>5267</v>
       </c>
@@ -4159,7 +4166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>5267</v>
       </c>
@@ -4176,7 +4183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>5267</v>
       </c>
@@ -4193,7 +4200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>5267</v>
       </c>
@@ -4210,7 +4217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>5267</v>
       </c>
@@ -4227,7 +4234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>5267</v>
       </c>
@@ -4244,7 +4251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>5267</v>
       </c>
@@ -4261,7 +4268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>5267</v>
       </c>
@@ -4278,7 +4285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>5267</v>
       </c>
@@ -4295,7 +4302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>5267</v>
       </c>
@@ -4312,7 +4319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>5267</v>
       </c>
@@ -4329,7 +4336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>5267</v>
       </c>
@@ -4346,7 +4353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>5267</v>
       </c>
@@ -4363,7 +4370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>5267</v>
       </c>
@@ -4380,7 +4387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>5338</v>
       </c>
@@ -4397,7 +4404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>5338</v>
       </c>
@@ -4414,7 +4421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>5338</v>
       </c>
@@ -4431,7 +4438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>5338</v>
       </c>
@@ -4448,7 +4455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>5338</v>
       </c>
@@ -4465,7 +4472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>5338</v>
       </c>
@@ -4482,7 +4489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>5338</v>
       </c>
@@ -4499,7 +4506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>5404</v>
       </c>
@@ -4516,7 +4523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>5404</v>
       </c>
@@ -4533,7 +4540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>5404</v>
       </c>
@@ -4550,7 +4557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>5404</v>
       </c>
@@ -4567,7 +4574,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>5404</v>
       </c>
@@ -4584,7 +4591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>5404</v>
       </c>
@@ -4601,7 +4608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>5404</v>
       </c>
@@ -4618,7 +4625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>5404</v>
       </c>
@@ -4635,7 +4642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>5761</v>
       </c>
@@ -4652,7 +4659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>5267</v>
       </c>
@@ -4669,7 +4676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>5267</v>
       </c>
@@ -4686,7 +4693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>5267</v>
       </c>
@@ -4703,7 +4710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>5267</v>
       </c>
@@ -4720,7 +4727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>5267</v>
       </c>
@@ -4737,7 +4744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>5267</v>
       </c>
@@ -4754,7 +4761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>5267</v>
       </c>
@@ -4771,7 +4778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>5267</v>
       </c>
@@ -4788,7 +4795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>5338</v>
       </c>
@@ -4805,7 +4812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>5338</v>
       </c>
@@ -4822,7 +4829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>5338</v>
       </c>
@@ -4839,7 +4846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>5338</v>
       </c>
@@ -4856,7 +4863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>5338</v>
       </c>
@@ -4873,7 +4880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>5338</v>
       </c>
@@ -4890,7 +4897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>5338</v>
       </c>
@@ -4907,7 +4914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>5338</v>
       </c>
@@ -4924,7 +4931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>6029</v>
       </c>
@@ -4941,7 +4948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>6029</v>
       </c>
@@ -4958,7 +4965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>6029</v>
       </c>
@@ -4975,7 +4982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>6029</v>
       </c>
@@ -4992,7 +4999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>6029</v>
       </c>
@@ -5009,7 +5016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>6029</v>
       </c>
@@ -5026,7 +5033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>6406</v>
       </c>
@@ -5043,7 +5050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>6406</v>
       </c>
@@ -5060,7 +5067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>6406</v>
       </c>
@@ -5077,7 +5084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>6406</v>
       </c>
@@ -5094,7 +5101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>5761</v>
       </c>
@@ -5111,7 +5118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>5761</v>
       </c>
@@ -5128,7 +5135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>6586</v>
       </c>
@@ -5145,7 +5152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>6586</v>
       </c>
@@ -5162,7 +5169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>6586</v>
       </c>
@@ -5179,7 +5186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>6586</v>
       </c>
@@ -5196,7 +5203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>6586</v>
       </c>
@@ -5213,7 +5220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>6586</v>
       </c>
@@ -5230,7 +5237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>6586</v>
       </c>
@@ -5247,7 +5254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>6586</v>
       </c>
@@ -5264,7 +5271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>6586</v>
       </c>
@@ -5281,7 +5288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>6586</v>
       </c>
@@ -5298,7 +5305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>6586</v>
       </c>
@@ -5315,7 +5322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>6586</v>
       </c>
@@ -5332,7 +5339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>5267</v>
       </c>
@@ -5349,7 +5356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>5267</v>
       </c>
@@ -5366,7 +5373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>5267</v>
       </c>
@@ -5383,7 +5390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>5267</v>
       </c>
@@ -5400,7 +5407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>5267</v>
       </c>
@@ -5417,7 +5424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>5338</v>
       </c>
@@ -5434,7 +5441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>5267</v>
       </c>
@@ -5451,7 +5458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>5267</v>
       </c>
@@ -5468,7 +5475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>5267</v>
       </c>
@@ -5485,7 +5492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>5267</v>
       </c>
@@ -5502,7 +5509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>5267</v>
       </c>
@@ -5519,7 +5526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>7158</v>
       </c>
@@ -5536,7 +5543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>7158</v>
       </c>
@@ -5553,7 +5560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>7158</v>
       </c>
@@ -5570,7 +5577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>7158</v>
       </c>
@@ -5587,7 +5594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>7224</v>
       </c>
@@ -5604,7 +5611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>7224</v>
       </c>
@@ -5621,7 +5628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>7224</v>
       </c>
@@ -5638,7 +5645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>7224</v>
       </c>
@@ -5655,7 +5662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>7224</v>
       </c>
@@ -5672,7 +5679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>7224</v>
       </c>
@@ -5689,7 +5696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>7224</v>
       </c>
@@ -5706,7 +5713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>7224</v>
       </c>
@@ -5723,7 +5730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>7224</v>
       </c>
@@ -5740,7 +5747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>7224</v>
       </c>
@@ -5757,7 +5764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>7224</v>
       </c>
@@ -5774,7 +5781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>7224</v>
       </c>
@@ -5791,7 +5798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>7224</v>
       </c>
@@ -5808,7 +5815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>7224</v>
       </c>
@@ -5825,7 +5832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>7224</v>
       </c>
@@ -5842,7 +5849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>7224</v>
       </c>
@@ -5859,7 +5866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>7224</v>
       </c>
@@ -5876,7 +5883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>7401</v>
       </c>
@@ -5893,7 +5900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>7401</v>
       </c>
@@ -5910,7 +5917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>6029</v>
       </c>
@@ -5927,7 +5934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>6029</v>
       </c>
@@ -5944,7 +5951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>6029</v>
       </c>
@@ -5961,7 +5968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>6029</v>
       </c>
@@ -5978,7 +5985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>6029</v>
       </c>
@@ -5995,7 +6002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>6029</v>
       </c>
@@ -6012,7 +6019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>5761</v>
       </c>
@@ -6029,7 +6036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>5761</v>
       </c>
@@ -6046,7 +6053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>6586</v>
       </c>
@@ -6063,7 +6070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>6586</v>
       </c>
@@ -6080,7 +6087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>6586</v>
       </c>
@@ -6097,7 +6104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>6586</v>
       </c>
@@ -6114,7 +6121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>6586</v>
       </c>
@@ -6131,7 +6138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>6586</v>
       </c>
@@ -6148,7 +6155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>6586</v>
       </c>
@@ -6165,7 +6172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>6586</v>
       </c>
@@ -6182,7 +6189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>6586</v>
       </c>
@@ -6199,7 +6206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>6586</v>
       </c>
@@ -6216,7 +6223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>6406</v>
       </c>
@@ -6233,7 +6240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>6406</v>
       </c>
@@ -6250,7 +6257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>6406</v>
       </c>
@@ -6267,7 +6274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>6406</v>
       </c>
@@ -6284,7 +6291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>7158</v>
       </c>
@@ -6301,7 +6308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>7158</v>
       </c>
@@ -6318,7 +6325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>7158</v>
       </c>
@@ -6335,7 +6342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>7158</v>
       </c>
@@ -6352,7 +6359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>7158</v>
       </c>
@@ -6369,7 +6376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>6406</v>
       </c>
@@ -6386,7 +6393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>5267</v>
       </c>
@@ -6403,7 +6410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>5267</v>
       </c>
@@ -6420,7 +6427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>5267</v>
       </c>
@@ -6437,7 +6444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>5338</v>
       </c>
@@ -6454,7 +6461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>5338</v>
       </c>
@@ -6471,7 +6478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>7224</v>
       </c>
@@ -6488,7 +6495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>7224</v>
       </c>
@@ -6505,7 +6512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>7224</v>
       </c>
@@ -6522,7 +6529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>7224</v>
       </c>
@@ -6539,7 +6546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>7224</v>
       </c>
@@ -6556,7 +6563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>7224</v>
       </c>
@@ -6573,7 +6580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>7224</v>
       </c>
@@ -6590,7 +6597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>7401</v>
       </c>
@@ -6607,7 +6614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>7401</v>
       </c>
@@ -6624,7 +6631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>7401</v>
       </c>
@@ -6641,7 +6648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>7401</v>
       </c>
@@ -6658,7 +6665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>7401</v>
       </c>
@@ -6675,7 +6682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>7401</v>
       </c>
@@ -6692,7 +6699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>7401</v>
       </c>
@@ -6709,7 +6716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>7401</v>
       </c>
@@ -6726,7 +6733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>7401</v>
       </c>
@@ -6743,7 +6750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>5267</v>
       </c>
@@ -6760,7 +6767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>5267</v>
       </c>
@@ -6777,7 +6784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>5267</v>
       </c>
@@ -6794,7 +6801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>5267</v>
       </c>
@@ -6811,7 +6818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>5267</v>
       </c>
@@ -6828,7 +6835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>5267</v>
       </c>
@@ -6845,7 +6852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>5267</v>
       </c>
@@ -6862,7 +6869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>7158</v>
       </c>
@@ -6879,7 +6886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>7158</v>
       </c>
@@ -6896,7 +6903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>7158</v>
       </c>
@@ -6913,7 +6920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>7158</v>
       </c>
@@ -6930,7 +6937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>7224</v>
       </c>
@@ -6947,7 +6954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>7224</v>
       </c>
@@ -6964,7 +6971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>7224</v>
       </c>
@@ -6981,7 +6988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>7224</v>
       </c>
@@ -6998,7 +7005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>7224</v>
       </c>
@@ -7015,7 +7022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>5763</v>
       </c>
@@ -7032,7 +7039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>5763</v>
       </c>
@@ -7049,7 +7056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>5763</v>
       </c>
@@ -7066,7 +7073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>5763</v>
       </c>
@@ -7083,7 +7090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>5763</v>
       </c>
@@ -7100,7 +7107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>5763</v>
       </c>
@@ -7117,7 +7124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>5763</v>
       </c>
@@ -7134,7 +7141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>5763</v>
       </c>
@@ -7151,7 +7158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>5763</v>
       </c>
@@ -7168,7 +7175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>5763</v>
       </c>
@@ -7185,7 +7192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>5763</v>
       </c>
@@ -7202,7 +7209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>5763</v>
       </c>
@@ -7219,7 +7226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>5763</v>
       </c>
@@ -7236,7 +7243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>5763</v>
       </c>
@@ -7253,7 +7260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>5826</v>
       </c>
@@ -7270,7 +7277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>5826</v>
       </c>
@@ -7287,7 +7294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>5826</v>
       </c>
@@ -7304,7 +7311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>5826</v>
       </c>
@@ -7321,7 +7328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>5826</v>
       </c>
@@ -7338,7 +7345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>5826</v>
       </c>
@@ -7355,7 +7362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>5826</v>
       </c>
@@ -7372,7 +7379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>5827</v>
       </c>
@@ -7389,7 +7396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>5827</v>
       </c>
@@ -7406,7 +7413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>5827</v>
       </c>
@@ -7423,7 +7430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>5827</v>
       </c>
@@ -7440,7 +7447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>5827</v>
       </c>
@@ -7457,7 +7464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>5827</v>
       </c>
@@ -7474,7 +7481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>5827</v>
       </c>
@@ -7491,7 +7498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>6163</v>
       </c>
@@ -7508,7 +7515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>5763</v>
       </c>
@@ -7525,7 +7532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>5763</v>
       </c>
@@ -7542,7 +7549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>5763</v>
       </c>
@@ -7559,7 +7566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>5763</v>
       </c>
@@ -7576,7 +7583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>5763</v>
       </c>
@@ -7593,7 +7600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>5826</v>
       </c>
@@ -7610,7 +7617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>5826</v>
       </c>
@@ -7627,7 +7634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>5826</v>
       </c>
@@ -7644,7 +7651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>5826</v>
       </c>
@@ -7661,7 +7668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>5826</v>
       </c>
@@ -7678,7 +7685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>5826</v>
       </c>
@@ -7695,7 +7702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>5826</v>
       </c>
@@ -7712,7 +7719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>6229</v>
       </c>
@@ -7729,7 +7736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>6229</v>
       </c>
@@ -7746,7 +7753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>6229</v>
       </c>
@@ -7763,7 +7770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>6229</v>
       </c>
@@ -7780,7 +7787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>6229</v>
       </c>
@@ -7797,7 +7804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>6588</v>
       </c>
@@ -7814,7 +7821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>6588</v>
       </c>
@@ -7831,7 +7838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>6588</v>
       </c>
@@ -7848,7 +7855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>6588</v>
       </c>
@@ -7865,7 +7872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>6588</v>
       </c>
@@ -7882,7 +7889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>6163</v>
       </c>
@@ -7899,7 +7906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>6821</v>
       </c>
@@ -7916,7 +7923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>6821</v>
       </c>
@@ -7933,7 +7940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>6821</v>
       </c>
@@ -7950,7 +7957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>6821</v>
       </c>
@@ -7967,7 +7974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>6821</v>
       </c>
@@ -7984,7 +7991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>6821</v>
       </c>
@@ -8001,7 +8008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>6821</v>
       </c>
@@ -8018,7 +8025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>6821</v>
       </c>
@@ -8035,7 +8042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>6821</v>
       </c>
@@ -8052,7 +8059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>6821</v>
       </c>
@@ -8069,7 +8076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>6821</v>
       </c>
@@ -8086,7 +8093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>5763</v>
       </c>
@@ -8103,7 +8110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>5763</v>
       </c>
@@ -8120,7 +8127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>5763</v>
       </c>
@@ -8137,7 +8144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>5763</v>
       </c>
@@ -8154,7 +8161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>5763</v>
       </c>
@@ -8171,7 +8178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>5826</v>
       </c>
@@ -8188,7 +8195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>5826</v>
       </c>
@@ -8205,7 +8212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>5826</v>
       </c>
@@ -8222,7 +8229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>5763</v>
       </c>
@@ -8239,7 +8246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>5763</v>
       </c>
@@ -8256,7 +8263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>5763</v>
       </c>
@@ -8273,7 +8280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>5763</v>
       </c>
@@ -8290,7 +8297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>7579</v>
       </c>
@@ -8307,7 +8314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>7579</v>
       </c>
@@ -8324,7 +8331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>7579</v>
       </c>
@@ -8341,7 +8348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>7579</v>
       </c>
@@ -8358,7 +8365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>7579</v>
       </c>
@@ -8375,7 +8382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>7581</v>
       </c>
@@ -8392,7 +8399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>7581</v>
       </c>
@@ -8409,7 +8416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>7581</v>
       </c>
@@ -8426,7 +8433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>7581</v>
       </c>
@@ -8443,7 +8450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>7581</v>
       </c>
@@ -8460,7 +8467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>7581</v>
       </c>
@@ -8477,7 +8484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>7581</v>
       </c>
@@ -8494,7 +8501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>7581</v>
       </c>
@@ -8511,7 +8518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>7581</v>
       </c>
@@ -8528,7 +8535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>7581</v>
       </c>
@@ -8545,7 +8552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>7581</v>
       </c>
@@ -8562,7 +8569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>7581</v>
       </c>
@@ -8579,7 +8586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>7581</v>
       </c>
@@ -8596,7 +8603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>7581</v>
       </c>
@@ -8613,7 +8620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>7583</v>
       </c>
@@ -8630,7 +8637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>7583</v>
       </c>
@@ -8647,7 +8654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>6229</v>
       </c>
@@ -8664,7 +8671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>6229</v>
       </c>
@@ -8681,7 +8688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>6229</v>
       </c>
@@ -8698,7 +8705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>6229</v>
       </c>
@@ -8715,7 +8722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>6229</v>
       </c>
@@ -8732,7 +8739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>6229</v>
       </c>
@@ -8749,7 +8756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>6229</v>
       </c>
@@ -8766,7 +8773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>6229</v>
       </c>
@@ -8783,7 +8790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>6163</v>
       </c>
@@ -8800,7 +8807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>6163</v>
       </c>
@@ -8817,7 +8824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>6821</v>
       </c>
@@ -8834,7 +8841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>6821</v>
       </c>
@@ -8851,7 +8858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>6821</v>
       </c>
@@ -8868,7 +8875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>6821</v>
       </c>
@@ -8885,7 +8892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>6821</v>
       </c>
@@ -8902,7 +8909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>6821</v>
       </c>
@@ -8919,7 +8926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>6821</v>
       </c>
@@ -8936,7 +8943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>6821</v>
       </c>
@@ -8953,7 +8960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>6821</v>
       </c>
@@ -8970,7 +8977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>6821</v>
       </c>
@@ -8987,7 +8994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>6588</v>
       </c>
@@ -9004,7 +9011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>6588</v>
       </c>
@@ -9021,7 +9028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>6588</v>
       </c>
@@ -9038,7 +9045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>6588</v>
       </c>
@@ -9055,7 +9062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>7579</v>
       </c>
@@ -9072,7 +9079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>7579</v>
       </c>
@@ -9089,7 +9096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>7579</v>
       </c>
@@ -9106,7 +9113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>7579</v>
       </c>
@@ -9123,7 +9130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>6588</v>
       </c>
@@ -9140,7 +9147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>5763</v>
       </c>
@@ -9157,7 +9164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>5763</v>
       </c>
@@ -9174,7 +9181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>5763</v>
       </c>
@@ -9192,6 +9199,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9199,15 +9207,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0C316B-CD9D-9B4A-8E4D-32ECAAF9A7E0}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -9221,7 +9229,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -9235,7 +9243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>37</v>
       </c>
@@ -9249,7 +9257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>38</v>
       </c>
@@ -9263,7 +9271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
@@ -9277,7 +9285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -9291,7 +9299,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -9305,7 +9313,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -9319,7 +9327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
@@ -9333,7 +9341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>44</v>
       </c>
@@ -9347,7 +9355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -9361,7 +9369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>46</v>
       </c>
@@ -9375,7 +9383,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>47</v>
       </c>
@@ -9389,7 +9397,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>48</v>
       </c>
@@ -9403,7 +9411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -9417,7 +9425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>50</v>
       </c>
@@ -9431,7 +9439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>51</v>
       </c>
@@ -9445,7 +9453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>52</v>
       </c>
@@ -9460,6 +9468,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9467,13 +9476,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2892F0D6-2B78-5043-9A0C-72B415817ECB}">
   <dimension ref="A1:B91"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -9481,7 +9490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>100520</v>
       </c>
@@ -9489,7 +9498,7 @@
         <v>44998.770138888889</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>100522</v>
       </c>
@@ -9497,7 +9506,7 @@
         <v>44998.927083333336</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100525</v>
       </c>
@@ -9505,7 +9514,7 @@
         <v>44999.417361111111</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>100527</v>
       </c>
@@ -9513,7 +9522,7 @@
         <v>44998.593055555553</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>100538</v>
       </c>
@@ -9521,7 +9530,7 @@
         <v>45006.515972222223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>100542</v>
       </c>
@@ -9529,7 +9538,7 @@
         <v>45006.811805555553</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>100549</v>
       </c>
@@ -9537,7 +9546,7 @@
         <v>45007.020833333336</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>100556</v>
       </c>
@@ -9545,7 +9554,7 @@
         <v>45007.293055555558</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>100579</v>
       </c>
@@ -9553,7 +9562,7 @@
         <v>45017.9375</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>100589</v>
       </c>
@@ -9561,7 +9570,7 @@
         <v>45018.708333333336</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>100789</v>
       </c>
@@ -9569,7 +9578,7 @@
         <v>45025.390972222223</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>100823</v>
       </c>
@@ -9577,7 +9586,7 @@
         <v>45028.647222222222</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>100824</v>
       </c>
@@ -9585,7 +9594,7 @@
         <v>45034.648611111108</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>100832</v>
       </c>
@@ -9593,7 +9602,7 @@
         <v>45038.688888888886</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>100934</v>
       </c>
@@ -9601,7 +9610,7 @@
         <v>45047.425000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>100976</v>
       </c>
@@ -9609,7 +9618,7 @@
         <v>45047.502083333333</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>100979</v>
       </c>
@@ -9617,7 +9626,7 @@
         <v>45047.526388888895</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>101923</v>
       </c>
@@ -9625,7 +9634,7 @@
         <v>45047.724305555559</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>101925</v>
       </c>
@@ -9633,7 +9642,7 @@
         <v>45049.722222222219</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>102092</v>
       </c>
@@ -9641,7 +9650,7 @@
         <v>45051.709722222222</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>102129</v>
       </c>
@@ -9649,7 +9658,7 @@
         <v>45051.334722222222</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>102139</v>
       </c>
@@ -9657,7 +9666,7 @@
         <v>45051.367361111115</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>102148</v>
       </c>
@@ -9665,7 +9674,7 @@
         <v>45054.69027777778</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>102152</v>
       </c>
@@ -9673,7 +9682,7 @@
         <v>45057.793749999997</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>102199</v>
       </c>
@@ -9681,7 +9690,7 @@
         <v>45058.56527777778</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>102293</v>
       </c>
@@ -9689,7 +9698,7 @@
         <v>45064.648611111108</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>102298</v>
       </c>
@@ -9697,7 +9706,7 @@
         <v>45066.552083333336</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>103012</v>
       </c>
@@ -9705,7 +9714,7 @@
         <v>45067.855555555558</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>103229</v>
       </c>
@@ -9713,7 +9722,7 @@
         <v>45068.974305555559</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>103291</v>
       </c>
@@ -9721,7 +9730,7 @@
         <v>45068.993750000009</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>103345</v>
       </c>
@@ -9729,7 +9738,7 @@
         <v>45069.263888888891</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>103376</v>
       </c>
@@ -9737,7 +9746,7 @@
         <v>45069.751388888886</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>103482</v>
       </c>
@@ -9745,7 +9754,7 @@
         <v>45069.904861111114</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>105087</v>
       </c>
@@ -9753,7 +9762,7 @@
         <v>45006.117361111108</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>105089</v>
       </c>
@@ -9761,7 +9770,7 @@
         <v>45006.274305555555</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>105092</v>
       </c>
@@ -9769,7 +9778,7 @@
         <v>45006.76458333333</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>105094</v>
       </c>
@@ -9777,7 +9786,7 @@
         <v>45005.940277777772</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>105105</v>
       </c>
@@ -9785,7 +9794,7 @@
         <v>45013.863194444442</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>105109</v>
       </c>
@@ -9793,7 +9802,7 @@
         <v>45014.159027777772</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>105116</v>
       </c>
@@ -9801,7 +9810,7 @@
         <v>45014.368055555555</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>105123</v>
       </c>
@@ -9809,7 +9818,7 @@
         <v>45014.640277777777</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>105146</v>
       </c>
@@ -9817,7 +9826,7 @@
         <v>45025.284722222219</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>105156</v>
       </c>
@@ -9825,7 +9834,7 @@
         <v>45026.055555555555</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>105356</v>
       </c>
@@ -9833,7 +9842,7 @@
         <v>45032.738194444442</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>105390</v>
       </c>
@@ -9841,7 +9850,7 @@
         <v>45035.994444444441</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>105391</v>
       </c>
@@ -9849,7 +9858,7 @@
         <v>45042.001736111102</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>105399</v>
       </c>
@@ -9857,7 +9866,7 @@
         <v>45046.036111111105</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>105501</v>
       </c>
@@ -9865,7 +9874,7 @@
         <v>45054.772222222222</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>105543</v>
       </c>
@@ -9873,7 +9882,7 @@
         <v>45054.849305555552</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>105546</v>
       </c>
@@ -9881,7 +9890,7 @@
         <v>45054.873611111114</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>106490</v>
       </c>
@@ -9889,7 +9898,7 @@
         <v>45055.071527777778</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>106492</v>
       </c>
@@ -9897,7 +9906,7 @@
         <v>45057.069444444438</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>106659</v>
       </c>
@@ -9905,7 +9914,7 @@
         <v>45059.056944444441</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>106696</v>
       </c>
@@ -9913,7 +9922,7 @@
         <v>45058.681944444441</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>106706</v>
       </c>
@@ -9921,7 +9930,7 @@
         <v>45058.714583333334</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>106715</v>
       </c>
@@ -9929,7 +9938,7 @@
         <v>45062.037499999999</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>106719</v>
       </c>
@@ -9937,7 +9946,7 @@
         <v>45065.140972222216</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>106766</v>
       </c>
@@ -9945,7 +9954,7 @@
         <v>45065.912499999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>106860</v>
       </c>
@@ -9953,7 +9962,7 @@
         <v>45071.995833333327</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>107579</v>
       </c>
@@ -9961,7 +9970,7 @@
         <v>45075.202777777777</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>107796</v>
       </c>
@@ -9969,7 +9978,7 @@
         <v>45076.321527777778</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>107858</v>
       </c>
@@ -9977,7 +9986,7 @@
         <v>45076.340972222228</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>107912</v>
       </c>
@@ -9985,7 +9994,7 @@
         <v>45076.611111111109</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>107943</v>
       </c>
@@ -9993,7 +10002,7 @@
         <v>45077.098611111105</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>108049</v>
       </c>
@@ -10001,7 +10010,7 @@
         <v>45077.252083333333</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>109654</v>
       </c>
@@ -10009,7 +10018,7 @@
         <v>45014.070138888892</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>109656</v>
       </c>
@@ -10017,7 +10026,7 @@
         <v>45014.231944444451</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>109659</v>
       </c>
@@ -10025,7 +10034,7 @@
         <v>45014.717361111114</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>109661</v>
       </c>
@@ -10033,7 +10042,7 @@
         <v>45013.893055555556</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>109672</v>
       </c>
@@ -10041,7 +10050,7 @@
         <v>45021.815972222226</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>109676</v>
       </c>
@@ -10049,7 +10058,7 @@
         <v>45022.111805555556</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>109683</v>
       </c>
@@ -10057,7 +10066,7 @@
         <v>45022.320833333339</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>109690</v>
       </c>
@@ -10065,7 +10074,7 @@
         <v>45022.593055555561</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>109713</v>
       </c>
@@ -10073,7 +10082,7 @@
         <v>45033.237500000003</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>109723</v>
       </c>
@@ -10081,7 +10090,7 @@
         <v>45034.008333333339</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>109923</v>
       </c>
@@ -10089,7 +10098,7 @@
         <v>45040.690972222226</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>109957</v>
       </c>
@@ -10097,7 +10106,7 @@
         <v>45043.947222222225</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>109958</v>
       </c>
@@ -10105,7 +10114,7 @@
         <v>45049.948611111111</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>109966</v>
       </c>
@@ -10113,7 +10122,7 @@
         <v>45053.988888888889</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>110068</v>
       </c>
@@ -10121,7 +10130,7 @@
         <v>45062.725000000006</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>110110</v>
       </c>
@@ -10129,7 +10138,7 @@
         <v>45062.802083333336</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>110113</v>
       </c>
@@ -10137,7 +10146,7 @@
         <v>45062.826388888898</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>111057</v>
       </c>
@@ -10145,7 +10154,7 @@
         <v>45063.024305555562</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>111059</v>
       </c>
@@ -10153,7 +10162,7 @@
         <v>45065.022222222222</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>111226</v>
       </c>
@@ -10161,7 +10170,7 @@
         <v>45067.009722222225</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>111263</v>
       </c>
@@ -10169,7 +10178,7 @@
         <v>45066.637152777781</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>111273</v>
       </c>
@@ -10177,7 +10186,7 @@
         <v>45066.667361111118</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>111282</v>
       </c>
@@ -10185,7 +10194,7 @@
         <v>45069.993750000001</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>111286</v>
       </c>
@@ -10193,7 +10202,7 @@
         <v>45073.09375</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>111333</v>
       </c>
@@ -10202,6 +10211,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>